--- a/Employee_Reports_wi48/Mark Jayson Rosima Q0265.xlsx
+++ b/Employee_Reports_wi48/Mark Jayson Rosima Q0265.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-322</v>
+        <v>-325</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-301</v>
+        <v>-304</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-405</v>
+        <v>-408</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1069,11 +1069,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-330</v>
+        <v>-333</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-330</v>
+        <v>-333</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1155,11 +1155,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1192,11 +1192,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1229,11 +1229,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
